--- a/artfynd/A 26324-2024 artfynd.xlsx
+++ b/artfynd/A 26324-2024 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110398661</v>
+        <v>113178100</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ammerberget, Jmt</t>
+          <t>Hällmyrorna, sydost om, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542585.479477233</v>
+        <v>542505</v>
       </c>
       <c r="R2" t="n">
-        <v>7018496.1580807</v>
+        <v>7018600</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,31 +756,43 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>äldre barrblandskog på frisk mark med blåbär</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>4 substratenheter # barkfallna äldre tallågor</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Louise Almén</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Louise Almén</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110398660</v>
+        <v>110398658</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -826,7 +819,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542587.9831558713</v>
+        <v>542541</v>
       </c>
       <c r="R3" t="n">
-        <v>7018545.229220313</v>
+        <v>7018619</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,19 +861,9 @@
           <t>2023-06-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110398658</v>
+        <v>110398660</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -942,7 +920,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -951,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542541.0644647265</v>
+        <v>542588</v>
       </c>
       <c r="R4" t="n">
-        <v>7018618.388705151</v>
+        <v>7018545</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,19 +962,9 @@
           <t>2023-06-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,50 +991,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113178100</v>
+        <v>110398661</v>
       </c>
       <c r="B5" t="n">
-        <v>95203</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hällmyrorna, sydost om, Jmt</t>
+          <t>Ammerberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542505</v>
+        <v>542586</v>
       </c>
       <c r="R5" t="n">
-        <v>7018600</v>
+        <v>7018496</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,12 +1060,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,36 +1076,19 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>äldre barrblandskog på frisk mark med blåbär</t>
-        </is>
-      </c>
-      <c r="AN5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>4 substratenheter # barkfallna äldre tallågor</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Louise Almén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Louise Almén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26324-2024 artfynd.xlsx
+++ b/artfynd/A 26324-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113178100</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110398658</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110398660</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,8 +1109,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110398661</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>